--- a/data/trans_camb/P20B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 22,38</t>
+          <t>-26,78; 23,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 40,87</t>
+          <t>-12,05; 41,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 26,56</t>
+          <t>-23,27; 27,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 16,52</t>
+          <t>-14,55; 16,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 24,44</t>
+          <t>-10,25; 27,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 21,2</t>
+          <t>-13,57; 21,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 14,17</t>
+          <t>-12,22; 14,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 27,85</t>
+          <t>-3,13; 27,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 19,18</t>
+          <t>-9,92; 19,4</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 130,89</t>
+          <t>-52,85; 160,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 269,75</t>
+          <t>-22,4; 278,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 177,35</t>
+          <t>-45,83; 170,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 118,89</t>
+          <t>-46,66; 117,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 161,02</t>
+          <t>-34,76; 174,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 150,24</t>
+          <t>-43,18; 154,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 78,48</t>
+          <t>-35,01; 83,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 153,86</t>
+          <t>-9,71; 148,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 107,73</t>
+          <t>-28,72; 105,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 22,17</t>
+          <t>-15,57; 20,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 25,07</t>
+          <t>-13,24; 22,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 21,66</t>
+          <t>-13,49; 20,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 26,86</t>
+          <t>0,94; 25,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 19,04</t>
+          <t>-6,08; 19,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 21,7</t>
+          <t>-3,12; 23,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 21,79</t>
+          <t>0,97; 21,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 16,51</t>
+          <t>-3,46; 16,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 18,43</t>
+          <t>-2,56; 18,28</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 215,65</t>
+          <t>-47,61; 178,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 230,22</t>
+          <t>-45,33; 178,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,19; 184,42</t>
+          <t>-46,45; 170,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 336,73</t>
+          <t>-1,84; 316,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 230,42</t>
+          <t>-34,83; 244,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 262,98</t>
+          <t>-21,32; 320,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 197,86</t>
+          <t>2,81; 195,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 150,15</t>
+          <t>-18,57; 150,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 168,93</t>
+          <t>-13,86; 160,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 33,93</t>
+          <t>-8,28; 33,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 35,17</t>
+          <t>-9,57; 37,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 38,89</t>
+          <t>-5,16; 38,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 9,1</t>
+          <t>-20,57; 9,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 14,45</t>
+          <t>-19,63; 14,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 3,43</t>
+          <t>-24,43; 4,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 14,22</t>
+          <t>-12,37; 13,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 16,44</t>
+          <t>-10,07; 14,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 14,3</t>
+          <t>-12,59; 14,51</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 270,93</t>
+          <t>-33,41; 286,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 284,97</t>
+          <t>-40,54; 276,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 361,98</t>
+          <t>-18,06; 339,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 42,65</t>
+          <t>-56,52; 54,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 71,14</t>
+          <t>-57,17; 82,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,1; 22,42</t>
+          <t>-70,39; 24,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 77,08</t>
+          <t>-35,88; 71,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 81,75</t>
+          <t>-33,27; 70,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 74,15</t>
+          <t>-35,65; 73,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 15,57</t>
+          <t>-21,34; 14,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 13,09</t>
+          <t>-23,51; 12,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 18,3</t>
+          <t>-16,14; 16,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 16,41</t>
+          <t>-9,8; 16,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 19,38</t>
+          <t>-8,47; 18,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 18,29</t>
+          <t>-7,11; 18,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 11,37</t>
+          <t>-10,96; 11,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 13,98</t>
+          <t>-7,59; 14,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 15,66</t>
+          <t>-5,76; 14,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,77; 76,99</t>
+          <t>-51,31; 65,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 66,93</t>
+          <t>-59,1; 57,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 86,87</t>
+          <t>-38,97; 76,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 151,31</t>
+          <t>-39,7; 143,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 183,36</t>
+          <t>-36,0; 155,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 157,61</t>
+          <t>-28,92; 170,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 68,13</t>
+          <t>-36,29; 66,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 79,16</t>
+          <t>-28,53; 76,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 90,72</t>
+          <t>-19,98; 82,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 13,26</t>
+          <t>-5,92; 13,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 17,68</t>
+          <t>-3,07; 17,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 16,72</t>
+          <t>-3,62; 16,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 11,25</t>
+          <t>-2,65; 11,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 11,06</t>
+          <t>-3,43; 12,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,37</t>
+          <t>-4,76; 9,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 9,97</t>
+          <t>-1,67; 10,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 11,73</t>
+          <t>-0,33; 11,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 11,33</t>
+          <t>-0,51; 11,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 62,52</t>
+          <t>-18,78; 65,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 80,31</t>
+          <t>-9,57; 86,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 85,3</t>
+          <t>-11,65; 75,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 71,67</t>
+          <t>-11,54; 68,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 67,62</t>
+          <t>-15,11; 75,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 56,77</t>
+          <t>-19,19; 58,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 50,26</t>
+          <t>-6,46; 52,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 60,56</t>
+          <t>-0,99; 61,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 58,96</t>
+          <t>-2,09; 57,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 23,56</t>
+          <t>-26,93; 24,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 41,43</t>
+          <t>-10,27; 42,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 27,14</t>
+          <t>-26,81; 25,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 16,53</t>
+          <t>-13,28; 16,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 27,1</t>
+          <t>-12,74; 23,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 21,16</t>
+          <t>-13,44; 21,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 14,59</t>
+          <t>-12,92; 13,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 27,78</t>
+          <t>-3,23; 27,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 19,4</t>
+          <t>-9,11; 18,52</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,85; 160,37</t>
+          <t>-53,31; 177,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 278,13</t>
+          <t>-20,22; 282,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,83; 170,49</t>
+          <t>-50,7; 195,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 117,18</t>
+          <t>-41,02; 128,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 174,24</t>
+          <t>-40,16; 150,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 154,84</t>
+          <t>-41,65; 142,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 83,95</t>
+          <t>-36,73; 74,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 148,39</t>
+          <t>-8,68; 157,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 105,35</t>
+          <t>-26,79; 102,52</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,35</t>
+          <t>8,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,63</t>
+          <t>9,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 20,28</t>
+          <t>-12,13; 21,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 22,7</t>
+          <t>-12,52; 25,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 20,37</t>
+          <t>-10,72; 26,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 25,81</t>
+          <t>0,43; 25,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 19,13</t>
+          <t>-5,89; 19,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 23,96</t>
+          <t>-2,74; 24,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 21,16</t>
+          <t>1,05; 20,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 16,79</t>
+          <t>-3,88; 16,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 18,28</t>
+          <t>-1,01; 20,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 178,33</t>
+          <t>-42,21; 192,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 178,27</t>
+          <t>-47,07; 237,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 170,75</t>
+          <t>-40,42; 240,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 316,64</t>
+          <t>-5,59; 300,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 244,26</t>
+          <t>-35,29; 233,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 320,76</t>
+          <t>-18,61; 289,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 195,07</t>
+          <t>3,51; 177,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 150,37</t>
+          <t>-18,69; 141,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 160,17</t>
+          <t>-9,15; 174,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,64</t>
+          <t>18,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,09</t>
+          <t>-10,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 33,33</t>
+          <t>-10,71; 30,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 37,18</t>
+          <t>-10,32; 36,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 38,94</t>
+          <t>-2,29; 39,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 9,62</t>
+          <t>-20,42; 9,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 14,95</t>
+          <t>-20,22; 12,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 4,6</t>
+          <t>-25,06; 3,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 13,84</t>
+          <t>-12,47; 13,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 14,59</t>
+          <t>-12,18; 15,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 14,51</t>
+          <t>-11,6; 15,63</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-38,17%</t>
+          <t>-36,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 286,69</t>
+          <t>-34,52; 245,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 276,23</t>
+          <t>-35,1; 296,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 339,72</t>
+          <t>-12,41; 350,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 54,41</t>
+          <t>-56,43; 47,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,17; 82,45</t>
+          <t>-57,34; 74,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,39; 24,89</t>
+          <t>-68,77; 19,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 71,44</t>
+          <t>-38,13; 68,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 70,77</t>
+          <t>-38,27; 68,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 73,16</t>
+          <t>-34,73; 80,08</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,32</t>
+          <t>6,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 14,18</t>
+          <t>-21,93; 14,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 12,73</t>
+          <t>-21,43; 14,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 16,99</t>
+          <t>-16,77; 16,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 16,32</t>
+          <t>-7,8; 17,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 18,1</t>
+          <t>-7,6; 20,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 18,46</t>
+          <t>-6,04; 17,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 11,96</t>
+          <t>-8,68; 12,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 14,04</t>
+          <t>-9,28; 13,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 14,34</t>
+          <t>-5,61; 13,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 65,34</t>
+          <t>-51,65; 72,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 57,12</t>
+          <t>-54,05; 70,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 76,74</t>
+          <t>-39,38; 85,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 143,3</t>
+          <t>-34,22; 158,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 155,7</t>
+          <t>-29,56; 191,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 170,56</t>
+          <t>-25,64; 163,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 66,85</t>
+          <t>-31,0; 69,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 76,74</t>
+          <t>-32,17; 78,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 82,28</t>
+          <t>-18,99; 79,57</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 13,3</t>
+          <t>-6,01; 12,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,54</t>
+          <t>-2,92; 18,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 16,01</t>
+          <t>-3,1; 16,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 11,62</t>
+          <t>-2,61; 11,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 12,17</t>
+          <t>-3,2; 12,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 9,78</t>
+          <t>-3,81; 10,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 10,1</t>
+          <t>-1,04; 9,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 11,75</t>
+          <t>-0,07; 12,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,17</t>
+          <t>-0,26; 11,18</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 65,53</t>
+          <t>-19,25; 59,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 86,94</t>
+          <t>-11,49; 83,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 75,41</t>
+          <t>-9,11; 84,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 68,51</t>
+          <t>-11,73; 70,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 75,03</t>
+          <t>-14,13; 72,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 58,48</t>
+          <t>-14,98; 61,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 52,8</t>
+          <t>-4,21; 50,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 61,44</t>
+          <t>-0,56; 63,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 57,33</t>
+          <t>-1,13; 56,77</t>
         </is>
       </c>
     </row>
